--- a/inputTemplate.xlsx
+++ b/inputTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cb404351ad199228/아티스트하우스_리포트/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\artisthouse_jj\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{50F8078E-BC25-4087-A262-266550C130A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{540A5125-F61C-455A-9B34-D16154307CFF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BFA74CE-1B09-44A0-9D0C-3199BF8704BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{976482D7-190D-4F44-BA22-6C43B7E902DA}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{976482D7-190D-4F44-BA22-6C43B7E902DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
   <si>
     <t>이름</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -137,8 +137,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>홍길동바보</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>홍길동 학생은 현재 모의 실기 80점, 내신 80점으로, 형태력과 성실한 완성도가 강점이며 영화고, 상명고 지원이 가능한 수준입니다. 작품을 깔끔하게 마무리하고 기본적인 구도를 잘 잡습니다. 그러나 최상위권인 연세고, 서울고 진학을 위해서는 독창적인 사고력과 세밀한 묘사 디테일 강화가 시급합니다. 주제를 평면적으로 해석하는 경향이 있으며, 시험 시 긴장으로 인한 실력 편차가 큽니다. 향후 전략: 앞으로 3개월간 주제를 다각도로 해석하는 '아이디어 발상 훈련'과 사물의 고유 질감을 살리는 '부분 묘사 클리닉'에 집중해야 합니다. 또한, 실전과 같은 환경에서 반복 훈련하여 멘탈 관리를 강화하면, 목표 학교에 도전할 수 있습니다.</t>
   </si>
 </sst>
 </file>
@@ -146,20 +145,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;;@"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -194,12 +193,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -214,12 +213,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -535,19 +530,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375FABDB-A463-4D92-AD67-7E4252EE219D}">
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="14.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="106.25" style="1" customWidth="1"/>
-    <col min="6" max="12" width="8.6640625" style="1"/>
-    <col min="13" max="14" width="29.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.64453125" style="1"/>
+    <col min="2" max="2" width="14.3515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.17578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.46875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="106.234375" style="1" customWidth="1"/>
+    <col min="6" max="12" width="8.64453125" style="1"/>
+    <col min="13" max="14" width="29.05859375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -591,7 +586,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="85">
+    <row r="2" spans="1:14" ht="67.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -635,7 +630,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="85">
+    <row r="3" spans="1:14" ht="54" x14ac:dyDescent="0.3">
       <c r="D3" s="2">
         <v>46023</v>
       </c>
@@ -670,7 +665,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" ht="67.5" x14ac:dyDescent="0.3">
       <c r="D4" s="2">
         <v>46068</v>
       </c>
@@ -702,6 +697,111 @@
         <v>18</v>
       </c>
       <c r="N4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="D5" s="2">
+        <v>46082</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="1">
+        <v>80</v>
+      </c>
+      <c r="G5" s="1">
+        <v>80</v>
+      </c>
+      <c r="H5" s="1">
+        <v>75</v>
+      </c>
+      <c r="I5" s="1">
+        <v>60</v>
+      </c>
+      <c r="J5" s="1">
+        <v>65</v>
+      </c>
+      <c r="K5" s="1">
+        <v>80</v>
+      </c>
+      <c r="L5" s="1">
+        <v>50</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="D6" s="2">
+        <v>46113</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="1">
+        <v>80</v>
+      </c>
+      <c r="G6" s="1">
+        <v>80</v>
+      </c>
+      <c r="H6" s="1">
+        <v>75</v>
+      </c>
+      <c r="I6" s="1">
+        <v>60</v>
+      </c>
+      <c r="J6" s="1">
+        <v>65</v>
+      </c>
+      <c r="K6" s="1">
+        <v>80</v>
+      </c>
+      <c r="L6" s="1">
+        <v>50</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="D7" s="2">
+        <v>46157</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="1">
+        <v>80</v>
+      </c>
+      <c r="G7" s="1">
+        <v>80</v>
+      </c>
+      <c r="H7" s="1">
+        <v>75</v>
+      </c>
+      <c r="I7" s="1">
+        <v>60</v>
+      </c>
+      <c r="J7" s="1">
+        <v>65</v>
+      </c>
+      <c r="K7" s="1">
+        <v>80</v>
+      </c>
+      <c r="L7" s="1">
+        <v>50</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>19</v>
       </c>
     </row>
